--- a/Results/example_run/design_log.example.xlsx
+++ b/Results/example_run/design_log.example.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,20 +574,25 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>compressor_reheat_factor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>combustor_equivalence_ratio</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>combustor_residence_time_ms</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>nozzle_choke_status</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>output_dir</t>
         </is>
@@ -596,12 +601,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260703_225709</t>
+          <t>20260703_231056</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-03T22:57:11</t>
+          <t>2026-07-03T23:10:58</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -689,19 +694,22 @@
         <v>0.1632395166818722</v>
       </c>
       <c r="AF2" t="n">
+        <v>1.050732399048704</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0.4109617988307843</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>0.5771650628692643</v>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>supersonic_at_throat</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>/Users/sanju/Projects/Propulsion/Gas Turbine Design Toolkit/Results/20260703_225709</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>/Users/sanju/Projects/Propulsion/Gas Turbine Design Toolkit/Results/20260703_231056</t>
         </is>
       </c>
     </row>
